--- a/plc/s7-1x00/core/adt/stack/EStackMethod-v1.0.xlsx
+++ b/plc/s7-1x00/core/adt/stack/EStackMethod-v1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PlcFramework\code\plc\s7-1x00\core\adt\stack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89D9028F-3AD3-431A-8DD6-E686F506845C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B877C88-C4E7-4515-ACA2-7AC57AA55A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18570" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="1" r:id="rId1"/>
@@ -91,17 +91,17 @@
     <t>Bool</t>
   </si>
   <si>
-    <t>{"version":"v1.0","author":"cyanezf","family":"core/adt/stack"}</t>
-  </si>
-  <si>
     <t>EStackMethod</t>
+  </si>
+  <si>
+    <t>{"version":"v1.0","author":"cyanezf","family":"core/adt/stack","status": "current", "deprecatedBy": null, "dependencies"  : []}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -464,7 +464,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.7265625" bestFit="1" customWidth="1"/>
@@ -473,7 +473,7 @@
     <col min="5" max="5" width="41.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -490,9 +490,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
@@ -504,10 +504,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -524,7 +524,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -558,7 +558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -575,7 +575,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>15</v>
       </c>
